--- a/data/trending_integrated_20261026_12.xlsx
+++ b/data/trending_integrated_20261026_12.xlsx
@@ -578,13 +578,13 @@
         <v>-0.34</v>
       </c>
       <c r="E2" t="n">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="F2" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="G2" t="n">
-        <v>467</v>
+        <v>494</v>
       </c>
       <c r="H2" t="n">
         <v>7.36</v>
@@ -610,7 +610,7 @@
         <v>7.7</v>
       </c>
       <c r="O2" t="n">
-        <v>58783178625</v>
+        <v>58810942725</v>
       </c>
       <c r="P2" t="n">
         <v>49800</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>AI 신약 밸류체인 합류 및 임상 진입, 연기금 순매수 기반 상승 기대.</t>
+          <t>공매도 세력의 대차 상환 압박 및 글로벌 AI 신약 밸류체인 합류. 빅파마와의 후기 임상 진입 기대.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['AI 신약', '연기금', '임상']</t>
+          <t>['공매도', 'AI 신약', '임상 진입']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2135</v>
+        <v>2110</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+9.83%</t>
+          <t>'+8.54%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.13</v>
       </c>
       <c r="E3" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F3" t="n">
         <v>34</v>
       </c>
       <c r="G3" t="n">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="H3" t="n">
         <v>5</v>
@@ -702,7 +702,7 @@
         <v>4.87</v>
       </c>
       <c r="O3" t="n">
-        <v>57148710736</v>
+        <v>57796187589</v>
       </c>
       <c r="P3" t="n">
         <v>4980</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5860</v>
+        <v>5920</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+6.74%</t>
+          <t>'+7.83%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.67</v>
       </c>
       <c r="E4" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F4" t="n">
         <v>47</v>
       </c>
       <c r="G4" t="n">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="H4" t="n">
         <v>2</v>
@@ -794,7 +794,7 @@
         <v>2.67</v>
       </c>
       <c r="O4" t="n">
-        <v>37066871665</v>
+        <v>37737209165</v>
       </c>
       <c r="P4" t="n">
         <v>7400</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>정치 테마주에 대한 부정적 전망 및 투자 경고.</t>
+          <t>정치 테마주에 대한 기대감과 경고. 특정 정치인의 지지율 상승 및 주가 상승 전망.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['정치 테마주', '지지율', '주가 전망']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1278000</v>
+        <v>1279000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+0.08%</t>
+          <t>'+0.16%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -857,10 +857,10 @@
         <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="G5" t="n">
-        <v>1659</v>
+        <v>1744</v>
       </c>
       <c r="H5" t="n">
         <v>48.69</v>
@@ -886,7 +886,7 @@
         <v>48.77</v>
       </c>
       <c r="O5" t="n">
-        <v>1780789834000</v>
+        <v>1818440829000</v>
       </c>
       <c r="P5" t="n">
         <v>2987000</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>주가 부양 의지 부족 및 시장 조작 의혹 제기, 데이터센터 전망.</t>
+          <t>특정 정치인의 행보에 따른 증시 하락 우려 및 개인 투자자들의 고통 호소. 외국인 매매 동향 주시.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['데이터센터', '주가조작']</t>
+          <t>['정치적 악재', '개인 투자자', '외국인']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,31 +931,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>213250</v>
+        <v>59200</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-1.04%</t>
+          <t>'-1.00%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.02</v>
+        <v>1.49</v>
       </c>
       <c r="E6" t="n">
-        <v>800</v>
+        <v>133</v>
       </c>
       <c r="F6" t="n">
-        <v>466</v>
+        <v>80</v>
       </c>
       <c r="G6" t="n">
-        <v>1486</v>
+        <v>584</v>
       </c>
       <c r="H6" t="n">
-        <v>46.11</v>
+        <v>40.39</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>215500</v>
+        <v>59800</v>
       </c>
       <c r="K6" t="n">
-        <v>213500</v>
+        <v>59400</v>
       </c>
       <c r="L6" t="n">
-        <v>216000</v>
+        <v>60200</v>
       </c>
       <c r="M6" t="n">
-        <v>211500</v>
+        <v>57700</v>
       </c>
       <c r="N6" t="n">
-        <v>46.13</v>
+        <v>38.9</v>
       </c>
       <c r="O6" t="n">
-        <v>1331953785750</v>
+        <v>168061340300</v>
       </c>
       <c r="P6" t="n">
-        <v>374500</v>
+        <v>67300</v>
       </c>
       <c r="Q6" t="n">
-        <v>94500</v>
+        <v>23150</v>
       </c>
       <c r="R6" t="n">
-        <v>-645000</v>
+        <v>352000</v>
       </c>
       <c r="S6" t="n">
-        <v>53000</v>
+        <v>16000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>현 정부 정책 및 경제 운영에 대한 비판과 불만.</t>
+          <t>공매도 세력에 대한 경고와 상승 기대감.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['공매도', '수급', '자사주']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>58900</v>
+        <v>213250</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-1.51%</t>
+          <t>'-1.04%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.49</v>
+        <v>-0.02</v>
       </c>
       <c r="E7" t="n">
-        <v>125</v>
+        <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>75</v>
+        <v>456</v>
       </c>
       <c r="G7" t="n">
-        <v>572</v>
+        <v>1547</v>
       </c>
       <c r="H7" t="n">
-        <v>40.39</v>
+        <v>46.11</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>59800</v>
+        <v>215500</v>
       </c>
       <c r="K7" t="n">
-        <v>59400</v>
+        <v>213500</v>
       </c>
       <c r="L7" t="n">
-        <v>60200</v>
+        <v>216000</v>
       </c>
       <c r="M7" t="n">
-        <v>57700</v>
+        <v>211500</v>
       </c>
       <c r="N7" t="n">
-        <v>38.9</v>
+        <v>46.13</v>
       </c>
       <c r="O7" t="n">
-        <v>163620655700</v>
+        <v>1358258543500</v>
       </c>
       <c r="P7" t="n">
-        <v>67300</v>
+        <v>374500</v>
       </c>
       <c r="Q7" t="n">
-        <v>23150</v>
+        <v>94500</v>
       </c>
       <c r="R7" t="n">
-        <v>352000</v>
+        <v>-645000</v>
       </c>
       <c r="S7" t="n">
-        <v>16000</v>
+        <v>53000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>공매도 세력에 대한 경고와 상승 기대감.</t>
+          <t>정치적 이슈 및 정부 정책에 대한 부정적 여론 형성. 경제 정책 실패 및 특정 정치인 비난.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['공매도', '수급', '자사주']</t>
+          <t>['정치', '경제 정책', '부정적 여론']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16440</v>
+        <v>16450</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-2.32%</t>
+          <t>'-2.26%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F8" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G8" t="n">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="H8" t="n">
         <v>27.94</v>
@@ -1162,7 +1162,7 @@
         <v>27.89</v>
       </c>
       <c r="O8" t="n">
-        <v>18647542375</v>
+        <v>19168866170</v>
       </c>
       <c r="P8" t="n">
         <v>35350</v>
@@ -1222,13 +1222,13 @@
         <v>-0.02</v>
       </c>
       <c r="E9" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F9" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G9" t="n">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="H9" t="n">
         <v>22.23</v>
@@ -1254,7 +1254,7 @@
         <v>22.25</v>
       </c>
       <c r="O9" t="n">
-        <v>46289208850</v>
+        <v>47596270850</v>
       </c>
       <c r="P9" t="n">
         <v>139200</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14180</v>
+        <v>14210</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-3.54%</t>
+          <t>'-3.33%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.14</v>
       </c>
       <c r="E10" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F10" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G10" t="n">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="H10" t="n">
         <v>10.03</v>
@@ -1346,7 +1346,7 @@
         <v>9.890000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>16572299170</v>
+        <v>16864885825</v>
       </c>
       <c r="P10" t="n">
         <v>40350</v>
@@ -1406,13 +1406,13 @@
         <v>0.05</v>
       </c>
       <c r="E11" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F11" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G11" t="n">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="H11" t="n">
         <v>12.39</v>
@@ -1438,7 +1438,7 @@
         <v>12.34</v>
       </c>
       <c r="O11" t="n">
-        <v>32727409925</v>
+        <v>33456044825</v>
       </c>
       <c r="P11" t="n">
         <v>59300</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3130</v>
+        <v>3120</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-17.85%</t>
+          <t>'-18.11%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="F12" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G12" t="n">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1530,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>21267002418</v>
+        <v>21607587651</v>
       </c>
       <c r="P12" t="n">
         <v>7050</v>

--- a/data/trending_integrated_20261026_12.xlsx
+++ b/data/trending_integrated_20261026_12.xlsx
@@ -581,10 +581,10 @@
         <v>149</v>
       </c>
       <c r="F2" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G2" t="n">
-        <v>494</v>
+        <v>517</v>
       </c>
       <c r="H2" t="n">
         <v>7.36</v>
@@ -610,7 +610,7 @@
         <v>7.7</v>
       </c>
       <c r="O2" t="n">
-        <v>58810942725</v>
+        <v>58834608315</v>
       </c>
       <c r="P2" t="n">
         <v>49800</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>공매도 세력의 대차 상환 압박 및 글로벌 AI 신약 밸류체인 합류. 빅파마와의 후기 임상 진입 기대.</t>
+          <t>AI 신약 개발 관련 긍정적 뉴스 및 기술력 언급. 빅파마 협력 및 임상 진입, 연기금 순매수 근거 제시. 공매도 상환 압박 및 숏 스퀴즈 기대.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['공매도', 'AI 신약', '임상 진입']</t>
+          <t>['AI 신약', '공매도', '연기금']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2110</v>
+        <v>2100</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+8.54%</t>
+          <t>'+8.02%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.13</v>
       </c>
       <c r="E3" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F3" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G3" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="H3" t="n">
         <v>5</v>
@@ -702,7 +702,7 @@
         <v>4.87</v>
       </c>
       <c r="O3" t="n">
-        <v>57796187589</v>
+        <v>59209819613</v>
       </c>
       <c r="P3" t="n">
         <v>4980</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5920</v>
+        <v>5730</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+7.83%</t>
+          <t>'+4.37%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.67</v>
       </c>
       <c r="E4" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F4" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G4" t="n">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="H4" t="n">
         <v>2</v>
@@ -794,7 +794,7 @@
         <v>2.67</v>
       </c>
       <c r="O4" t="n">
-        <v>37737209165</v>
+        <v>38062153735</v>
       </c>
       <c r="P4" t="n">
         <v>7400</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>정치 테마주에 대한 기대감과 경고. 특정 정치인의 지지율 상승 및 주가 상승 전망.</t>
+          <t>정치 테마 관련 언급. 지지율 변화 및 시세 관련 기대감 혼재. 근거 빈약.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['정치 테마주', '지지율', '주가 전망']</t>
+          <t>['정치 테마']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1279000</v>
+        <v>1275000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+0.16%</t>
+          <t>'-0.16%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -857,10 +857,10 @@
         <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="G5" t="n">
-        <v>1744</v>
+        <v>1818</v>
       </c>
       <c r="H5" t="n">
         <v>48.69</v>
@@ -886,7 +886,7 @@
         <v>48.77</v>
       </c>
       <c r="O5" t="n">
-        <v>1818440829000</v>
+        <v>1846377587000</v>
       </c>
       <c r="P5" t="n">
         <v>2987000</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>특정 정치인의 행보에 따른 증시 하락 우려 및 개인 투자자들의 고통 호소. 외국인 매매 동향 주시.</t>
+          <t>정치권 및 시장 상황에 대한 불만과 부정적 전망. 실적 발표 후 주가 하락 예상. 구체적 근거 부족.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['정치적 악재', '개인 투자자', '외국인']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,31 +931,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>59200</v>
+        <v>212500</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-1.00%</t>
+          <t>'-1.39%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.49</v>
+        <v>-0.02</v>
       </c>
       <c r="E6" t="n">
-        <v>133</v>
+        <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>80</v>
+        <v>452</v>
       </c>
       <c r="G6" t="n">
-        <v>584</v>
+        <v>1532</v>
       </c>
       <c r="H6" t="n">
-        <v>40.39</v>
+        <v>46.11</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>59800</v>
+        <v>215500</v>
       </c>
       <c r="K6" t="n">
-        <v>59400</v>
+        <v>213500</v>
       </c>
       <c r="L6" t="n">
-        <v>60200</v>
+        <v>216000</v>
       </c>
       <c r="M6" t="n">
-        <v>57700</v>
+        <v>211500</v>
       </c>
       <c r="N6" t="n">
-        <v>38.9</v>
+        <v>46.13</v>
       </c>
       <c r="O6" t="n">
-        <v>168061340300</v>
+        <v>1390673621500</v>
       </c>
       <c r="P6" t="n">
-        <v>67300</v>
+        <v>374500</v>
       </c>
       <c r="Q6" t="n">
-        <v>23150</v>
+        <v>94500</v>
       </c>
       <c r="R6" t="n">
-        <v>352000</v>
+        <v>-645000</v>
       </c>
       <c r="S6" t="n">
-        <v>16000</v>
+        <v>53000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>공매도 세력에 대한 경고와 상승 기대감.</t>
+          <t>정치적 이슈에 대한 강한 부정적 언급. 경제 정책 비판. 주가 관련 직접적 근거 없음.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['공매도', '수급', '자사주']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>213250</v>
+        <v>58900</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-1.04%</t>
+          <t>'-1.51%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.02</v>
+        <v>1.49</v>
       </c>
       <c r="E7" t="n">
-        <v>800</v>
+        <v>135</v>
       </c>
       <c r="F7" t="n">
-        <v>456</v>
+        <v>81</v>
       </c>
       <c r="G7" t="n">
-        <v>1547</v>
+        <v>616</v>
       </c>
       <c r="H7" t="n">
-        <v>46.11</v>
+        <v>40.39</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>215500</v>
+        <v>59800</v>
       </c>
       <c r="K7" t="n">
-        <v>213500</v>
+        <v>59400</v>
       </c>
       <c r="L7" t="n">
-        <v>216000</v>
+        <v>60200</v>
       </c>
       <c r="M7" t="n">
-        <v>211500</v>
+        <v>57700</v>
       </c>
       <c r="N7" t="n">
-        <v>46.13</v>
+        <v>38.9</v>
       </c>
       <c r="O7" t="n">
-        <v>1358258543500</v>
+        <v>172675503900</v>
       </c>
       <c r="P7" t="n">
-        <v>374500</v>
+        <v>67300</v>
       </c>
       <c r="Q7" t="n">
-        <v>94500</v>
+        <v>23150</v>
       </c>
       <c r="R7" t="n">
-        <v>-645000</v>
+        <v>352000</v>
       </c>
       <c r="S7" t="n">
-        <v>53000</v>
+        <v>16000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>정치적 이슈 및 정부 정책에 대한 부정적 여론 형성. 경제 정책 실패 및 특정 정치인 비난.</t>
+          <t>단기 급등 기대감 및 기술적 분석 언급. 수급 및 유동성 장세 활용 가능성 제시. 중동 전쟁 변수 포함.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['정치', '경제 정책', '부정적 여론']</t>
+          <t>['기술적 분석', '수급']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16450</v>
+        <v>16440</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-2.26%</t>
+          <t>'-2.32%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F8" t="n">
         <v>44</v>
       </c>
       <c r="G8" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H8" t="n">
         <v>27.94</v>
@@ -1162,7 +1162,7 @@
         <v>27.89</v>
       </c>
       <c r="O8" t="n">
-        <v>19168866170</v>
+        <v>19509224200</v>
       </c>
       <c r="P8" t="n">
         <v>35350</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>57900</v>
+        <v>57800</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-2.53%</t>
+          <t>'-2.69%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.02</v>
       </c>
       <c r="E9" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F9" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G9" t="n">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="H9" t="n">
         <v>22.23</v>
@@ -1254,7 +1254,7 @@
         <v>22.25</v>
       </c>
       <c r="O9" t="n">
-        <v>47596270850</v>
+        <v>48575568250</v>
       </c>
       <c r="P9" t="n">
         <v>139200</v>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14210</v>
+        <v>14200</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-3.33%</t>
+          <t>'-3.40%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1320,7 +1320,7 @@
         <v>42</v>
       </c>
       <c r="G10" t="n">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="H10" t="n">
         <v>10.03</v>
@@ -1346,7 +1346,7 @@
         <v>9.890000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>16864885825</v>
+        <v>17287832325</v>
       </c>
       <c r="P10" t="n">
         <v>40350</v>
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>27100</v>
+        <v>27050</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-4.75%</t>
+          <t>'-4.92%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1412,7 +1412,7 @@
         <v>47</v>
       </c>
       <c r="G11" t="n">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="H11" t="n">
         <v>12.39</v>
@@ -1438,7 +1438,7 @@
         <v>12.34</v>
       </c>
       <c r="O11" t="n">
-        <v>33456044825</v>
+        <v>34298091375</v>
       </c>
       <c r="P11" t="n">
         <v>59300</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3120</v>
+        <v>3110</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-18.11%</t>
+          <t>'-18.37%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="F12" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G12" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1524,13 +1524,13 @@
         <v>3555</v>
       </c>
       <c r="M12" t="n">
-        <v>3080</v>
+        <v>3070</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>21607587651</v>
+        <v>21980633248</v>
       </c>
       <c r="P12" t="n">
         <v>7050</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>북한 관련 이슈에 따른 급락 및 투자 심리 위축.</t>
+          <t>북한 관련 지정학적 리스크 언급. 주가 폭락 및 급락 예측. 전쟁 관련 기대감과 부정적 전망 혼재.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['자주포', '핵실험']</t>
+          <t>['지정학적 리스크', '전쟁']</t>
         </is>
       </c>
       <c r="X12" t="n">

--- a/data/trending_integrated_20261026_12.xlsx
+++ b/data/trending_integrated_20261026_12.xlsx
@@ -578,13 +578,13 @@
         <v>-0.34</v>
       </c>
       <c r="E2" t="n">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F2" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="G2" t="n">
-        <v>517</v>
+        <v>529</v>
       </c>
       <c r="H2" t="n">
         <v>7.36</v>
@@ -610,7 +610,7 @@
         <v>7.7</v>
       </c>
       <c r="O2" t="n">
-        <v>58834608315</v>
+        <v>58841395095</v>
       </c>
       <c r="P2" t="n">
         <v>49800</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>AI 신약 개발 관련 긍정적 뉴스 및 기술력 언급. 빅파마 협력 및 임상 진입, 연기금 순매수 근거 제시. 공매도 상환 압박 및 숏 스퀴즈 기대.</t>
+          <t>공매도 세력의 상환 가능성과 신규 임상 진입 등 긍정적 뉴스를 기반으로 한 강한 상승 기대.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['AI 신약', '공매도', '연기금']</t>
+          <t>['공매도', '신약', '밸류체인']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2100</v>
+        <v>2095</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+8.02%</t>
+          <t>'+7.77%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.13</v>
       </c>
       <c r="E3" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F3" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G3" t="n">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="H3" t="n">
         <v>5</v>
@@ -702,7 +702,7 @@
         <v>4.87</v>
       </c>
       <c r="O3" t="n">
-        <v>59209819613</v>
+        <v>59886055430</v>
       </c>
       <c r="P3" t="n">
         <v>4980</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5730</v>
+        <v>5890</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+4.37%</t>
+          <t>'+7.29%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.67</v>
       </c>
       <c r="E4" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F4" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G4" t="n">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="H4" t="n">
         <v>2</v>
@@ -794,7 +794,7 @@
         <v>2.67</v>
       </c>
       <c r="O4" t="n">
-        <v>38062153735</v>
+        <v>38596985245</v>
       </c>
       <c r="P4" t="n">
         <v>7400</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>정치 테마 관련 언급. 지지율 변화 및 시세 관련 기대감 혼재. 근거 빈약.</t>
+          <t>정치 테마주 관련 언급이 다수 있으나, 실제 주가 전망에 대한 구체적 근거 부족.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['정치 테마']</t>
+          <t>['정치 테마주', '개미', '우상향']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1275000</v>
+        <v>1272000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'-0.16%</t>
+          <t>'-0.39%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -860,7 +860,7 @@
         <v>469</v>
       </c>
       <c r="G5" t="n">
-        <v>1818</v>
+        <v>1837</v>
       </c>
       <c r="H5" t="n">
         <v>48.69</v>
@@ -886,7 +886,7 @@
         <v>48.77</v>
       </c>
       <c r="O5" t="n">
-        <v>1846377587000</v>
+        <v>1863350991000</v>
       </c>
       <c r="P5" t="n">
         <v>2987000</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>정치권 및 시장 상황에 대한 불만과 부정적 전망. 실적 발표 후 주가 하락 예상. 구체적 근거 부족.</t>
+          <t>정치적 요인과 연관된 부정적 언급이 많으며, 실적 발표에 대한 불안감 내포.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['이재명', '코스닥', '실적 발표']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,31 +931,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>212500</v>
+        <v>59000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-1.39%</t>
+          <t>'-1.34%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.02</v>
+        <v>1.49</v>
       </c>
       <c r="E6" t="n">
-        <v>800</v>
+        <v>137</v>
       </c>
       <c r="F6" t="n">
-        <v>452</v>
+        <v>82</v>
       </c>
       <c r="G6" t="n">
-        <v>1532</v>
+        <v>626</v>
       </c>
       <c r="H6" t="n">
-        <v>46.11</v>
+        <v>40.39</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>215500</v>
+        <v>59800</v>
       </c>
       <c r="K6" t="n">
-        <v>213500</v>
+        <v>59400</v>
       </c>
       <c r="L6" t="n">
-        <v>216000</v>
+        <v>60200</v>
       </c>
       <c r="M6" t="n">
-        <v>211500</v>
+        <v>57700</v>
       </c>
       <c r="N6" t="n">
-        <v>46.13</v>
+        <v>38.9</v>
       </c>
       <c r="O6" t="n">
-        <v>1390673621500</v>
+        <v>177789867200</v>
       </c>
       <c r="P6" t="n">
-        <v>374500</v>
+        <v>67300</v>
       </c>
       <c r="Q6" t="n">
-        <v>94500</v>
+        <v>23150</v>
       </c>
       <c r="R6" t="n">
-        <v>-645000</v>
+        <v>352000</v>
       </c>
       <c r="S6" t="n">
-        <v>53000</v>
+        <v>16000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>정치적 이슈에 대한 강한 부정적 언급. 경제 정책 비판. 주가 관련 직접적 근거 없음.</t>
+          <t>단기 급등 기대감 및 기술적 분석 언급. 수급 및 유동성 장세 활용 가능성 제시. 중동 전쟁 변수 포함.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['기술적 분석', '수급']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>58900</v>
+        <v>212500</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-1.51%</t>
+          <t>'-1.39%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.49</v>
+        <v>-0.02</v>
       </c>
       <c r="E7" t="n">
-        <v>135</v>
+        <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>81</v>
+        <v>452</v>
       </c>
       <c r="G7" t="n">
-        <v>616</v>
+        <v>1632</v>
       </c>
       <c r="H7" t="n">
-        <v>40.39</v>
+        <v>46.11</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>59800</v>
+        <v>215500</v>
       </c>
       <c r="K7" t="n">
-        <v>59400</v>
+        <v>213500</v>
       </c>
       <c r="L7" t="n">
-        <v>60200</v>
+        <v>216000</v>
       </c>
       <c r="M7" t="n">
-        <v>57700</v>
+        <v>211500</v>
       </c>
       <c r="N7" t="n">
-        <v>38.9</v>
+        <v>46.13</v>
       </c>
       <c r="O7" t="n">
-        <v>172675503900</v>
+        <v>1402410795750</v>
       </c>
       <c r="P7" t="n">
-        <v>67300</v>
+        <v>374500</v>
       </c>
       <c r="Q7" t="n">
-        <v>23150</v>
+        <v>94500</v>
       </c>
       <c r="R7" t="n">
-        <v>352000</v>
+        <v>-645000</v>
       </c>
       <c r="S7" t="n">
-        <v>16000</v>
+        <v>53000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>단기 급등 기대감 및 기술적 분석 언급. 수급 및 유동성 장세 활용 가능성 제시. 중동 전쟁 변수 포함.</t>
+          <t>정치 관련 부정적 내용으로 일관되며, 주가 관련 객관적 근거 부재.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['기술적 분석', '수급']</t>
+          <t>['이재명', '정부', '증시']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16440</v>
+        <v>16430</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-2.32%</t>
+          <t>'-2.38%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1162,7 +1162,7 @@
         <v>27.89</v>
       </c>
       <c r="O8" t="n">
-        <v>19509224200</v>
+        <v>19873510740</v>
       </c>
       <c r="P8" t="n">
         <v>35350</v>
@@ -1222,13 +1222,13 @@
         <v>-0.02</v>
       </c>
       <c r="E9" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F9" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G9" t="n">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="H9" t="n">
         <v>22.23</v>
@@ -1254,7 +1254,7 @@
         <v>22.25</v>
       </c>
       <c r="O9" t="n">
-        <v>48575568250</v>
+        <v>49088622750</v>
       </c>
       <c r="P9" t="n">
         <v>139200</v>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14200</v>
+        <v>14180</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-3.40%</t>
+          <t>'-3.54%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1320,7 +1320,7 @@
         <v>42</v>
       </c>
       <c r="G10" t="n">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="H10" t="n">
         <v>10.03</v>
@@ -1346,7 +1346,7 @@
         <v>9.890000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>17287832325</v>
+        <v>17754454095</v>
       </c>
       <c r="P10" t="n">
         <v>40350</v>
@@ -1406,13 +1406,13 @@
         <v>0.05</v>
       </c>
       <c r="E11" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F11" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G11" t="n">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="H11" t="n">
         <v>12.39</v>
@@ -1438,7 +1438,7 @@
         <v>12.34</v>
       </c>
       <c r="O11" t="n">
-        <v>34298091375</v>
+        <v>34744604225</v>
       </c>
       <c r="P11" t="n">
         <v>59300</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3110</v>
+        <v>3080</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-18.37%</t>
+          <t>'-19.16%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F12" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G12" t="n">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1530,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>21980633248</v>
+        <v>22183759758</v>
       </c>
       <c r="P12" t="n">
         <v>7050</v>

--- a/data/trending_integrated_20261026_12.xlsx
+++ b/data/trending_integrated_20261026_12.xlsx
@@ -578,13 +578,13 @@
         <v>-0.34</v>
       </c>
       <c r="E2" t="n">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="F2" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G2" t="n">
-        <v>529</v>
+        <v>544</v>
       </c>
       <c r="H2" t="n">
         <v>7.36</v>
@@ -610,7 +610,7 @@
         <v>7.7</v>
       </c>
       <c r="O2" t="n">
-        <v>58841395095</v>
+        <v>58932326195</v>
       </c>
       <c r="P2" t="n">
         <v>49800</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2095</v>
+        <v>2062</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+7.77%</t>
+          <t>'+6.07%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.13</v>
       </c>
       <c r="E3" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F3" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G3" t="n">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="H3" t="n">
         <v>5</v>
@@ -702,7 +702,7 @@
         <v>4.87</v>
       </c>
       <c r="O3" t="n">
-        <v>59886055430</v>
+        <v>60485097136</v>
       </c>
       <c r="P3" t="n">
         <v>4980</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5890</v>
+        <v>5820</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+7.29%</t>
+          <t>'+6.01%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.67</v>
       </c>
       <c r="E4" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F4" t="n">
         <v>50</v>
       </c>
       <c r="G4" t="n">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="H4" t="n">
         <v>2</v>
@@ -794,7 +794,7 @@
         <v>2.67</v>
       </c>
       <c r="O4" t="n">
-        <v>38596985245</v>
+        <v>38811864250</v>
       </c>
       <c r="P4" t="n">
         <v>7400</v>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1272000</v>
+        <v>1277000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'-0.39%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -857,7 +857,7 @@
         <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="G5" t="n">
         <v>1837</v>
@@ -886,7 +886,7 @@
         <v>48.77</v>
       </c>
       <c r="O5" t="n">
-        <v>1863350991000</v>
+        <v>1891910880000</v>
       </c>
       <c r="P5" t="n">
         <v>2987000</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>정치적 요인과 연관된 부정적 언급이 많으며, 실적 발표에 대한 불안감 내포.</t>
+          <t>정치적 이슈와 관련된 부정적 언급이 많으며, 주가 상승에 대한 기대감은 낮게 나타남.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['이재명', '코스닥', '실적 발표']</t>
+          <t>['정치적 이슈', '주가 하락', '실적 발표']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>59000</v>
+        <v>59300</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-1.34%</t>
+          <t>'-0.84%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>1.49</v>
       </c>
       <c r="E6" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F6" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G6" t="n">
-        <v>626</v>
+        <v>646</v>
       </c>
       <c r="H6" t="n">
         <v>40.39</v>
@@ -978,7 +978,7 @@
         <v>38.9</v>
       </c>
       <c r="O6" t="n">
-        <v>177789867200</v>
+        <v>182511679000</v>
       </c>
       <c r="P6" t="n">
         <v>67300</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>단기 급등 기대감 및 기술적 분석 언급. 수급 및 유동성 장세 활용 가능성 제시. 중동 전쟁 변수 포함.</t>
+          <t>주가 상승에 대한 강한 기대감과 공매도 세력에 대한 부정적 인식이 혼재함. 기술적 분석 및 수급 동향 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['기술적 분석', '수급']</t>
+          <t>['기술적 분석', '수급 동향', '공매도']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>212500</v>
+        <v>213500</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-1.39%</t>
+          <t>'-0.93%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1041,10 +1041,10 @@
         <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="G7" t="n">
-        <v>1632</v>
+        <v>1676</v>
       </c>
       <c r="H7" t="n">
         <v>46.11</v>
@@ -1070,7 +1070,7 @@
         <v>46.13</v>
       </c>
       <c r="O7" t="n">
-        <v>1402410795750</v>
+        <v>1441923699750</v>
       </c>
       <c r="P7" t="n">
         <v>374500</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>정치 관련 부정적 내용으로 일관되며, 주가 관련 객관적 근거 부재.</t>
+          <t>이재명 정부의 경제 정책에 대한 강한 비판과 부정적 전망이 주된 내용임.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['이재명', '정부', '증시']</t>
+          <t>['이재명', '경제 정책', '비판']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16430</v>
+        <v>16460</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-2.38%</t>
+          <t>'-2.20%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="F8" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G8" t="n">
         <v>184</v>
@@ -1162,7 +1162,7 @@
         <v>27.89</v>
       </c>
       <c r="O8" t="n">
-        <v>19873510740</v>
+        <v>20950280925</v>
       </c>
       <c r="P8" t="n">
         <v>35350</v>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>57800</v>
+        <v>58000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-2.69%</t>
+          <t>'-2.36%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1228,7 +1228,7 @@
         <v>110</v>
       </c>
       <c r="G9" t="n">
-        <v>504</v>
+        <v>515</v>
       </c>
       <c r="H9" t="n">
         <v>22.23</v>
@@ -1254,7 +1254,7 @@
         <v>22.25</v>
       </c>
       <c r="O9" t="n">
-        <v>49088622750</v>
+        <v>50707458250</v>
       </c>
       <c r="P9" t="n">
         <v>139200</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14180</v>
+        <v>14250</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-3.54%</t>
+          <t>'-3.06%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.14</v>
       </c>
       <c r="E10" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F10" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G10" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="H10" t="n">
         <v>10.03</v>
@@ -1346,7 +1346,7 @@
         <v>9.890000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>17754454095</v>
+        <v>18149541615</v>
       </c>
       <c r="P10" t="n">
         <v>40350</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>27050</v>
+        <v>27250</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-4.92%</t>
+          <t>'-4.22%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.05</v>
       </c>
       <c r="E11" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F11" t="n">
         <v>46</v>
       </c>
       <c r="G11" t="n">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H11" t="n">
         <v>12.39</v>
@@ -1438,7 +1438,7 @@
         <v>12.34</v>
       </c>
       <c r="O11" t="n">
-        <v>34744604225</v>
+        <v>35797580975</v>
       </c>
       <c r="P11" t="n">
         <v>59300</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3080</v>
+        <v>3050</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-19.16%</t>
+          <t>'-19.95%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="F12" t="n">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="G12" t="n">
-        <v>365</v>
+        <v>389</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1524,13 +1524,13 @@
         <v>3555</v>
       </c>
       <c r="M12" t="n">
-        <v>3070</v>
+        <v>3050</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>22183759758</v>
+        <v>22814903213</v>
       </c>
       <c r="P12" t="n">
         <v>7050</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>북한 관련 지정학적 리스크 언급. 주가 폭락 및 급락 예측. 전쟁 관련 기대감과 부정적 전망 혼재.</t>
+          <t>김정은 관련 이슈와 전쟁 가능성에 대한 언급이 있으며, 주가 급락에 대한 불안감이 나타남. 투기적 거래 가능성 제기.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['지정학적 리스크', '전쟁']</t>
+          <t>['김정은', '전쟁 가능성', '주가 급락']</t>
         </is>
       </c>
       <c r="X12" t="n">

--- a/data/trending_integrated_20261026_12.xlsx
+++ b/data/trending_integrated_20261026_12.xlsx
@@ -578,13 +578,13 @@
         <v>-0.34</v>
       </c>
       <c r="E2" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F2" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G2" t="n">
-        <v>544</v>
+        <v>558</v>
       </c>
       <c r="H2" t="n">
         <v>7.36</v>
@@ -610,7 +610,7 @@
         <v>7.7</v>
       </c>
       <c r="O2" t="n">
-        <v>58932326195</v>
+        <v>58937614595</v>
       </c>
       <c r="P2" t="n">
         <v>49800</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>공매도 세력의 상환 가능성과 신규 임상 진입 등 긍정적 뉴스를 기반으로 한 강한 상승 기대.</t>
+          <t>공매도 세력의 대차 상환 가능성 및 스퀴즈 랠리 기대. 글로벌 AI 신약 밸류체인 합류 및 빅파마와 후기 임상 진입 뉴스 기반 긍정적 전망.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['공매도', '신약', '밸류체인']</t>
+          <t>['공매도', 'AI 신약', '임상']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,184 +655,184 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>앤로보틱스</t>
+          <t>진양산업</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2062</v>
+        <v>5840</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+6.07%</t>
+          <t>'+6.38%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.13</v>
+        <v>-0.67</v>
       </c>
       <c r="E3" t="n">
-        <v>65</v>
+        <v>131</v>
       </c>
       <c r="F3" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="G3" t="n">
-        <v>131</v>
+        <v>159</v>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>1944</v>
+        <v>5490</v>
       </c>
       <c r="K3" t="n">
-        <v>2100</v>
+        <v>6250</v>
       </c>
       <c r="L3" t="n">
-        <v>2325</v>
+        <v>6340</v>
       </c>
       <c r="M3" t="n">
-        <v>2035</v>
+        <v>5470</v>
       </c>
       <c r="N3" t="n">
-        <v>4.87</v>
+        <v>2.67</v>
       </c>
       <c r="O3" t="n">
-        <v>60485097136</v>
+        <v>39316642990</v>
       </c>
       <c r="P3" t="n">
-        <v>4980</v>
+        <v>7400</v>
       </c>
       <c r="Q3" t="n">
-        <v>749</v>
+        <v>3660</v>
       </c>
       <c r="R3" t="n">
-        <v>89000</v>
+        <v>41000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>로봇 섹터 강세 및 신용/단타 투자자 퇴출 언급. 기술적 분석 기반 긍정적 흐름 기대.</t>
+          <t>정치 테마주 관련 언급이 다수 있으나, 실제 주가 전망에 대한 구체적 근거 부족.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['로봇 섹터', '단타', '기술적 분석']</t>
+          <t>['정치 테마주', '개미', '우상향']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>138360</t>
+          <t>003780</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>진양산업</t>
+          <t>앤로보틱스</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5820</v>
+        <v>2040</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+6.01%</t>
+          <t>'+4.94%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.67</v>
+        <v>0.13</v>
       </c>
       <c r="E4" t="n">
-        <v>127</v>
+        <v>66</v>
       </c>
       <c r="F4" t="n">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="G4" t="n">
-        <v>158</v>
+        <v>135</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>5490</v>
+        <v>1944</v>
       </c>
       <c r="K4" t="n">
-        <v>6250</v>
+        <v>2100</v>
       </c>
       <c r="L4" t="n">
-        <v>6340</v>
+        <v>2325</v>
       </c>
       <c r="M4" t="n">
-        <v>5470</v>
+        <v>2035</v>
       </c>
       <c r="N4" t="n">
-        <v>2.67</v>
+        <v>4.87</v>
       </c>
       <c r="O4" t="n">
-        <v>38811864250</v>
+        <v>61022559455</v>
       </c>
       <c r="P4" t="n">
-        <v>7400</v>
+        <v>4980</v>
       </c>
       <c r="Q4" t="n">
-        <v>3660</v>
+        <v>749</v>
       </c>
       <c r="R4" t="n">
-        <v>41000</v>
+        <v>89000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>정치 테마주 관련 언급이 다수 있으나, 실제 주가 전망에 대한 구체적 근거 부족.</t>
+          <t>로봇 섹터 강세 및 신용/단타 투자자 퇴출 언급. 기술적 분석 기반 긍정적 흐름 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['정치 테마주', '개미', '우상향']</t>
+          <t>['로봇 섹터', '단타', '기술적 분석']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>003780</t>
+          <t>138360</t>
         </is>
       </c>
     </row>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1277000</v>
+        <v>1282000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+0.00%</t>
+          <t>'+0.39%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -857,10 +857,10 @@
         <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="G5" t="n">
-        <v>1837</v>
+        <v>1874</v>
       </c>
       <c r="H5" t="n">
         <v>48.69</v>
@@ -886,7 +886,7 @@
         <v>48.77</v>
       </c>
       <c r="O5" t="n">
-        <v>1891910880000</v>
+        <v>1917496083000</v>
       </c>
       <c r="P5" t="n">
         <v>2987000</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>정치적 이슈와 관련된 부정적 언급이 많으며, 주가 상승에 대한 기대감은 낮게 나타남.</t>
+          <t>정치적 요인에 대한 부정적 언급으로 인한 코스닥 지수 및 개별 종목 하락 우려. 실적 발표에 대한 불확실성.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['정치적 이슈', '주가 하락', '실적 발표']</t>
+          <t>['정치', '실적', '하락']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>59300</v>
+        <v>59500</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-0.84%</t>
+          <t>'-0.50%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>1.49</v>
       </c>
       <c r="E6" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F6" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G6" t="n">
-        <v>646</v>
+        <v>665</v>
       </c>
       <c r="H6" t="n">
         <v>40.39</v>
@@ -978,7 +978,7 @@
         <v>38.9</v>
       </c>
       <c r="O6" t="n">
-        <v>182511679000</v>
+        <v>187368078850</v>
       </c>
       <c r="P6" t="n">
         <v>67300</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>주가 상승에 대한 강한 기대감과 공매도 세력에 대한 부정적 인식이 혼재함. 기술적 분석 및 수급 동향 언급.</t>
+          <t>공매도 세력에 대한 경계 속 기술적 분석 기반 매수 기회 포착. 유동성 장세 및 수급 동향 긍정적 전망.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['기술적 분석', '수급 동향', '공매도']</t>
+          <t>['공매도', '기술적 분석', '수급']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1041,10 +1041,10 @@
         <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="G7" t="n">
-        <v>1676</v>
+        <v>1758</v>
       </c>
       <c r="H7" t="n">
         <v>46.11</v>
@@ -1070,7 +1070,7 @@
         <v>46.13</v>
       </c>
       <c r="O7" t="n">
-        <v>1441923699750</v>
+        <v>1464954754750</v>
       </c>
       <c r="P7" t="n">
         <v>374500</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>이재명 정부의 경제 정책에 대한 강한 비판과 부정적 전망이 주된 내용임.</t>
+          <t>정치적 이슈에 대한 부정적 언급으로 인한 주가 하락 우려. 정부 정책 비판.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['이재명', '경제 정책', '비판']</t>
+          <t>['정치', '정책', '하락']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,18 +1119,18 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16460</v>
+        <v>16500</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-2.20%</t>
+          <t>'-1.96%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F8" t="n">
         <v>46</v>
@@ -1162,7 +1162,7 @@
         <v>27.89</v>
       </c>
       <c r="O8" t="n">
-        <v>20950280925</v>
+        <v>21604618735</v>
       </c>
       <c r="P8" t="n">
         <v>35350</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>58000</v>
+        <v>58100</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-2.36%</t>
+          <t>'-2.19%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.02</v>
       </c>
       <c r="E9" t="n">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F9" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="G9" t="n">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="H9" t="n">
         <v>22.23</v>
@@ -1254,7 +1254,7 @@
         <v>22.25</v>
       </c>
       <c r="O9" t="n">
-        <v>50707458250</v>
+        <v>51786807550</v>
       </c>
       <c r="P9" t="n">
         <v>139200</v>
@@ -1303,18 +1303,18 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14250</v>
+        <v>14280</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-3.06%</t>
+          <t>'-2.86%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.14</v>
       </c>
       <c r="E10" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F10" t="n">
         <v>41</v>
@@ -1346,7 +1346,7 @@
         <v>9.890000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>18149541615</v>
+        <v>18340160395</v>
       </c>
       <c r="P10" t="n">
         <v>40350</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>27250</v>
+        <v>27300</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-4.22%</t>
+          <t>'-4.04%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.05</v>
       </c>
       <c r="E11" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F11" t="n">
         <v>46</v>
       </c>
       <c r="G11" t="n">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="H11" t="n">
         <v>12.39</v>
@@ -1438,7 +1438,7 @@
         <v>12.34</v>
       </c>
       <c r="O11" t="n">
-        <v>35797580975</v>
+        <v>36785565400</v>
       </c>
       <c r="P11" t="n">
         <v>59300</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3050</v>
+        <v>3075</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-19.95%</t>
+          <t>'-19.29%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="F12" t="n">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="G12" t="n">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1524,13 +1524,13 @@
         <v>3555</v>
       </c>
       <c r="M12" t="n">
-        <v>3050</v>
+        <v>3035</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>22814903213</v>
+        <v>23200697765</v>
       </c>
       <c r="P12" t="n">
         <v>7050</v>
